--- a/data/paternity-table/paternity_table.xlsx
+++ b/data/paternity-table/paternity_table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosenbas/Documents/GitHub/primate-paternity-metanalysis/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rosenbas/Documents/GitHub/primate-paternity-metanalysis/data/paternity-table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CAA0805-7525-6E45-AD11-DDDAE4529CDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C21BB8F4-0978-144C-A9BF-24340FB54F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5160" yWindow="600" windowWidth="27120" windowHeight="20980" xr2:uid="{BC0DBF6F-2B3A-6448-9951-BEC3714F806A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5857" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5857" uniqueCount="854">
   <si>
     <t>Entry number</t>
   </si>
@@ -2296,9 +2296,6 @@
     <t>Yes (group type not applicable; rank not applicable)</t>
   </si>
   <si>
-    <t>Orangutan</t>
-  </si>
-  <si>
     <t>Pongo pygmaeus</t>
   </si>
   <si>
@@ -2621,6 +2618,12 @@
   </si>
   <si>
     <t xml:space="preserve">For this entry 'Number attributed to alpha or primary' contains information about offspring sired by flanged males; 'number attributed to other residents' contains information about unflanged males; and 'Number that cannot be assigned as either resident or EGP' refers to cases in which a specific father was assigned but his flange status as of the date of conception was unknown. Behavioral data/monitoring occurred from 1989 to 2000, but all fecal samples were collected between 2000 and 2002. Data also summarized in Scott et al 2024. </t>
+  </si>
+  <si>
+    <t>Borean orangutan</t>
+  </si>
+  <si>
+    <t>Sumatran orangutan</t>
   </si>
 </sst>
 </file>
@@ -3366,16 +3369,16 @@
         <v>715</v>
       </c>
       <c r="H1" s="30" t="s">
+        <v>778</v>
+      </c>
+      <c r="I1" s="30" t="s">
         <v>779</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="J1" s="30" t="s">
         <v>780</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="K1" s="30" t="s">
         <v>781</v>
-      </c>
-      <c r="K1" s="30" t="s">
-        <v>782</v>
       </c>
       <c r="L1" s="30" t="s">
         <v>3</v>
@@ -3551,16 +3554,16 @@
       <c r="F2" s="60"/>
       <c r="G2" s="60"/>
       <c r="H2" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I2" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="J2" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J2" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K2" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L2" s="35" t="s">
         <v>334</v>
@@ -3695,16 +3698,16 @@
       <c r="F3" s="60"/>
       <c r="G3" s="60"/>
       <c r="H3" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I3" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I3" s="60" t="s">
+      <c r="J3" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J3" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K3" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L3" s="35" t="s">
         <v>334</v>
@@ -3831,16 +3834,16 @@
       <c r="F4" s="60"/>
       <c r="G4" s="60"/>
       <c r="H4" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I4" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I4" s="60" t="s">
+      <c r="J4" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J4" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K4" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L4" s="35" t="s">
         <v>334</v>
@@ -3963,16 +3966,16 @@
       </c>
       <c r="E5" s="7"/>
       <c r="H5" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I5" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I5" s="60" t="s">
+      <c r="J5" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J5" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K5" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>198</v>
@@ -4073,16 +4076,16 @@
       </c>
       <c r="E6" s="7"/>
       <c r="H6" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I6" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I6" s="60" t="s">
+      <c r="J6" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J6" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K6" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>198</v>
@@ -4182,22 +4185,22 @@
         <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I7" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I7" s="60" t="s">
+      <c r="J7" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J7" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K7" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>307</v>
@@ -4309,7 +4312,7 @@
         <v>2006</v>
       </c>
       <c r="BK7" s="2" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="8" spans="1:66" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.2">
@@ -4329,16 +4332,16 @@
         <v>24</v>
       </c>
       <c r="H8" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I8" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I8" s="60" t="s">
+      <c r="J8" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J8" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K8" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>307</v>
@@ -4462,16 +4465,16 @@
         <v>24</v>
       </c>
       <c r="H9" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I9" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I9" s="60" t="s">
+      <c r="J9" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J9" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K9" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>307</v>
@@ -4586,13 +4589,13 @@
       </c>
       <c r="E10" s="7"/>
       <c r="H10" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>790</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>210</v>
@@ -4687,16 +4690,16 @@
       </c>
       <c r="E11" s="7"/>
       <c r="H11" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I11" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I11" s="60" t="s">
+      <c r="J11" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J11" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K11" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>182</v>
@@ -4790,16 +4793,16 @@
       </c>
       <c r="E12" s="7"/>
       <c r="H12" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I12" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I12" s="60" t="s">
+      <c r="J12" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J12" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K12" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L12" s="5" t="s">
         <v>182</v>
@@ -4893,16 +4896,16 @@
       </c>
       <c r="E13" s="7"/>
       <c r="H13" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I13" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I13" s="60" t="s">
+      <c r="J13" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J13" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K13" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L13" s="5" t="s">
         <v>182</v>
@@ -4993,16 +4996,16 @@
       </c>
       <c r="E14" s="7"/>
       <c r="H14" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I14" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I14" s="60" t="s">
+      <c r="J14" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J14" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K14" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L14" s="5" t="s">
         <v>182</v>
@@ -5096,16 +5099,16 @@
       </c>
       <c r="E15" s="7"/>
       <c r="H15" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I15" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I15" s="60" t="s">
+      <c r="J15" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J15" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K15" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L15" s="5" t="s">
         <v>182</v>
@@ -5196,16 +5199,16 @@
       </c>
       <c r="E16" s="7"/>
       <c r="H16" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I16" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I16" s="60" t="s">
+      <c r="J16" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J16" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K16" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L16" s="5" t="s">
         <v>182</v>
@@ -5293,16 +5296,16 @@
       </c>
       <c r="E17" s="7"/>
       <c r="H17" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I17" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I17" s="60" t="s">
+      <c r="J17" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J17" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K17" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L17" s="5" t="s">
         <v>182</v>
@@ -5390,16 +5393,16 @@
       </c>
       <c r="E18" s="7"/>
       <c r="H18" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I18" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I18" s="60" t="s">
+      <c r="J18" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J18" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K18" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L18" s="5" t="s">
         <v>182</v>
@@ -5495,16 +5498,16 @@
         <v>714</v>
       </c>
       <c r="H19" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I19" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I19" s="60" t="s">
+      <c r="J19" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J19" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K19" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L19" s="5" t="s">
         <v>161</v>
@@ -5649,16 +5652,16 @@
         <v>714</v>
       </c>
       <c r="H20" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I20" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I20" s="60" t="s">
+      <c r="J20" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J20" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K20" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L20" s="5" t="s">
         <v>161</v>
@@ -5805,16 +5808,16 @@
         <v>714</v>
       </c>
       <c r="H21" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I21" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I21" s="60" t="s">
+      <c r="J21" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J21" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K21" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L21" s="5" t="s">
         <v>161</v>
@@ -5955,16 +5958,16 @@
         <v>714</v>
       </c>
       <c r="H22" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I22" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I22" s="60" t="s">
+      <c r="J22" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J22" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K22" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L22" s="5" t="s">
         <v>161</v>
@@ -6099,16 +6102,16 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I23" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I23" s="60" t="s">
+      <c r="J23" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J23" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K23" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L23" s="5" t="s">
         <v>280</v>
@@ -6130,7 +6133,7 @@
         <v>282</v>
       </c>
       <c r="S23" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="T23" s="5" t="s">
         <v>283</v>
@@ -6231,16 +6234,16 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I24" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I24" s="60" t="s">
+      <c r="J24" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J24" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K24" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>378</v>
@@ -6352,7 +6355,7 @@
         <v>24</v>
       </c>
       <c r="E25" s="70" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F25" s="71" t="s">
         <v>38</v>
@@ -6361,16 +6364,16 @@
         <v>714</v>
       </c>
       <c r="H25" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I25" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I25" s="60" t="s">
+      <c r="J25" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J25" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K25" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L25" s="68" t="s">
         <v>347</v>
@@ -6386,7 +6389,7 @@
       </c>
       <c r="P25" s="68"/>
       <c r="Q25" s="68" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="R25" s="68" t="s">
         <v>349</v>
@@ -6500,7 +6503,7 @@
         <v>24</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F26" s="11" t="s">
         <v>38</v>
@@ -6509,16 +6512,16 @@
         <v>714</v>
       </c>
       <c r="H26" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I26" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I26" s="60" t="s">
+      <c r="J26" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J26" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K26" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L26" s="12" t="s">
         <v>347</v>
@@ -6534,7 +6537,7 @@
       </c>
       <c r="P26" s="12"/>
       <c r="Q26" s="12" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="R26" s="12" t="s">
         <v>349</v>
@@ -6651,16 +6654,16 @@
       </c>
       <c r="E27" s="7"/>
       <c r="H27" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I27" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I27" s="60" t="s">
+      <c r="J27" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J27" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K27" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L27" s="5" t="s">
         <v>233</v>
@@ -6756,16 +6759,16 @@
       </c>
       <c r="E28" s="7"/>
       <c r="H28" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I28" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I28" s="60" t="s">
+      <c r="J28" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J28" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K28" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L28" s="5" t="s">
         <v>233</v>
@@ -6858,16 +6861,16 @@
       </c>
       <c r="E29" s="7"/>
       <c r="H29" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I29" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I29" s="60" t="s">
+      <c r="J29" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J29" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K29" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L29" s="5" t="s">
         <v>233</v>
@@ -6954,16 +6957,16 @@
       </c>
       <c r="E30" s="7"/>
       <c r="H30" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I30" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I30" s="60" t="s">
+      <c r="J30" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J30" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K30" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L30" s="5" t="s">
         <v>233</v>
@@ -7049,16 +7052,16 @@
         <v>38</v>
       </c>
       <c r="H31" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I31" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I31" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J31" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L31" s="5" t="s">
         <v>388</v>
@@ -7154,16 +7157,16 @@
         <v>38</v>
       </c>
       <c r="H32" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I32" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I32" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J32" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L32" s="5" t="s">
         <v>388</v>
@@ -7260,16 +7263,16 @@
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
       <c r="H33" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I33" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I33" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J33" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L33" s="5" t="s">
         <v>388</v>
@@ -7390,16 +7393,16 @@
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I34" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I34" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J34" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L34" s="5" t="s">
         <v>388</v>
@@ -7522,16 +7525,16 @@
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I35" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I35" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J35" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L35" s="5" t="s">
         <v>388</v>
@@ -7656,16 +7659,16 @@
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I36" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I36" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J36" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K36" s="7" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L36" s="5" t="s">
         <v>435</v>
@@ -7792,14 +7795,14 @@
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="60" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="J37" s="7"/>
       <c r="K37" s="7" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="L37" s="7" t="s">
         <v>553</v>
@@ -7928,16 +7931,16 @@
       </c>
       <c r="E38" s="7"/>
       <c r="H38" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I38" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I38" s="60" t="s">
+      <c r="J38" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J38" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K38" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L38" s="5" t="s">
         <v>233</v>
@@ -8036,16 +8039,16 @@
         <v>38</v>
       </c>
       <c r="H39" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I39" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I39" s="60" t="s">
+      <c r="J39" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J39" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K39" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L39" s="5" t="s">
         <v>266</v>
@@ -8161,16 +8164,16 @@
         <v>38</v>
       </c>
       <c r="H40" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I40" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I40" s="60" t="s">
+      <c r="J40" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J40" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K40" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L40" s="5" t="s">
         <v>266</v>
@@ -8305,16 +8308,16 @@
         <v>38</v>
       </c>
       <c r="H41" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I41" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I41" s="60" t="s">
+      <c r="J41" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J41" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K41" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L41" s="5" t="s">
         <v>266</v>
@@ -8445,16 +8448,16 @@
         <v>38</v>
       </c>
       <c r="H42" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I42" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I42" s="60" t="s">
+      <c r="J42" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J42" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K42" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>266</v>
@@ -8548,7 +8551,7 @@
         <v>24</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>38</v>
@@ -8557,13 +8560,13 @@
         <v>714</v>
       </c>
       <c r="H43" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I43" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I43" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K43" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L43" s="7" t="s">
         <v>107</v>
@@ -8652,7 +8655,7 @@
         <v>2000</v>
       </c>
       <c r="BK43" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="44" spans="1:66" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.2">
@@ -8670,16 +8673,16 @@
       </c>
       <c r="E44" s="7"/>
       <c r="H44" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I44" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I44" s="60" t="s">
+      <c r="J44" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J44" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K44" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L44" s="7" t="s">
         <v>124</v>
@@ -8792,16 +8795,16 @@
       </c>
       <c r="E45" s="7"/>
       <c r="H45" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I45" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I45" s="60" t="s">
+      <c r="J45" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J45" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K45" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L45" s="7" t="s">
         <v>124</v>
@@ -8918,16 +8921,16 @@
       </c>
       <c r="E46" s="7"/>
       <c r="H46" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I46" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I46" s="60" t="s">
+      <c r="J46" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J46" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K46" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L46" s="7" t="s">
         <v>124</v>
@@ -9041,16 +9044,16 @@
       </c>
       <c r="E47" s="7"/>
       <c r="H47" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I47" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I47" s="60" t="s">
+      <c r="J47" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J47" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K47" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L47" s="7" t="s">
         <v>124</v>
@@ -9162,16 +9165,16 @@
         <v>38</v>
       </c>
       <c r="H48" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I48" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I48" s="60" t="s">
+      <c r="J48" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J48" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K48" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>182</v>
@@ -9265,16 +9268,16 @@
         <v>38</v>
       </c>
       <c r="H49" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I49" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I49" s="60" t="s">
+      <c r="J49" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J49" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K49" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>182</v>
@@ -9368,16 +9371,16 @@
         <v>38</v>
       </c>
       <c r="H50" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I50" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I50" s="60" t="s">
+      <c r="J50" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J50" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K50" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>182</v>
@@ -9471,16 +9474,16 @@
         <v>38</v>
       </c>
       <c r="H51" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I51" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I51" s="60" t="s">
+      <c r="J51" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J51" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K51" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>182</v>
@@ -9576,16 +9579,16 @@
         <v>38</v>
       </c>
       <c r="H52" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I52" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I52" s="60" t="s">
+      <c r="J52" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J52" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K52" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L52" s="5" t="s">
         <v>293</v>
@@ -9688,7 +9691,7 @@
         <v>24</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>38</v>
@@ -9697,16 +9700,16 @@
         <v>714</v>
       </c>
       <c r="H53" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I53" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I53" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J53" s="60" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L53" s="5" t="s">
         <v>83</v>
@@ -9793,7 +9796,7 @@
         <v>2016</v>
       </c>
       <c r="BK53" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="54" spans="1:66" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.2">
@@ -9810,23 +9813,23 @@
         <v>24</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I54" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I54" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J54" s="60" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L54" s="5" t="s">
         <v>83</v>
@@ -9918,7 +9921,7 @@
         <v>2016</v>
       </c>
       <c r="BK54" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="55" spans="1:66" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.2">
@@ -9932,7 +9935,7 @@
         <v>24</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>38</v>
@@ -9941,16 +9944,16 @@
         <v>714</v>
       </c>
       <c r="H55" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I55" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I55" s="60" t="s">
+      <c r="J55" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J55" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K55" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>378</v>
@@ -9971,10 +9974,10 @@
         <v>263</v>
       </c>
       <c r="S55" s="5" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="T55" s="5" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="U55" s="5" t="s">
         <v>48</v>
@@ -10052,16 +10055,16 @@
         <v>38</v>
       </c>
       <c r="H56" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I56" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I56" s="60" t="s">
+      <c r="J56" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J56" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K56" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L56" s="5" t="s">
         <v>243</v>
@@ -10163,16 +10166,16 @@
         <v>38</v>
       </c>
       <c r="H57" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I57" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I57" s="60" t="s">
+      <c r="J57" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J57" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K57" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L57" s="5" t="s">
         <v>243</v>
@@ -10281,16 +10284,16 @@
         <v>714</v>
       </c>
       <c r="H58" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I58" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I58" s="60" t="s">
+      <c r="J58" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J58" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K58" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L58" s="5" t="s">
         <v>417</v>
@@ -10421,16 +10424,16 @@
       <c r="F59" s="7"/>
       <c r="G59" s="7"/>
       <c r="H59" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I59" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I59" s="60" t="s">
+      <c r="J59" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J59" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K59" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L59" s="7" t="s">
         <v>266</v>
@@ -10565,16 +10568,16 @@
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
       <c r="H60" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I60" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I60" s="60" t="s">
+      <c r="J60" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J60" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K60" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L60" s="7" t="s">
         <v>266</v>
@@ -10709,16 +10712,16 @@
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
       <c r="H61" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I61" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I61" s="60" t="s">
+      <c r="J61" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J61" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K61" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="L61" s="7" t="s">
         <v>671</v>
@@ -10847,16 +10850,16 @@
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
       <c r="H62" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I62" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I62" s="60" t="s">
+      <c r="J62" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J62" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K62" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="L62" s="7" t="s">
         <v>671</v>
@@ -10983,16 +10986,16 @@
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
       <c r="H63" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I63" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I63" s="60" t="s">
+      <c r="J63" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J63" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K63" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="L63" s="7" t="s">
         <v>671</v>
@@ -11117,16 +11120,16 @@
         <v>38</v>
       </c>
       <c r="H64" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I64" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I64" s="60" t="s">
+      <c r="J64" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J64" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K64" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L64" s="5" t="s">
         <v>352</v>
@@ -11233,16 +11236,16 @@
         <v>38</v>
       </c>
       <c r="H65" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I65" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I65" s="60" t="s">
+      <c r="J65" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J65" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K65" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L65" s="5" t="s">
         <v>352</v>
@@ -11350,16 +11353,16 @@
         <v>38</v>
       </c>
       <c r="H66" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I66" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I66" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J66" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L66" s="5" t="s">
         <v>399</v>
@@ -11462,16 +11465,16 @@
         <v>38</v>
       </c>
       <c r="H67" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I67" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I67" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J67" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L67" s="5" t="s">
         <v>399</v>
@@ -11571,16 +11574,16 @@
         <v>38</v>
       </c>
       <c r="H68" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I68" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I68" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J68" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L68" s="5" t="s">
         <v>399</v>
@@ -11681,16 +11684,16 @@
         <v>38</v>
       </c>
       <c r="H69" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I69" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I69" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J69" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L69" s="5" t="s">
         <v>399</v>
@@ -11793,16 +11796,16 @@
         <v>38</v>
       </c>
       <c r="H70" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I70" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I70" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J70" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L70" s="5" t="s">
         <v>399</v>
@@ -11902,16 +11905,16 @@
         <v>38</v>
       </c>
       <c r="H71" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I71" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I71" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J71" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L71" s="5" t="s">
         <v>399</v>
@@ -12011,16 +12014,16 @@
         <v>38</v>
       </c>
       <c r="H72" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I72" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I72" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J72" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L72" s="5" t="s">
         <v>399</v>
@@ -12129,16 +12132,16 @@
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
       <c r="H73" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I73" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I73" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J73" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K73" s="7" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L73" s="5" t="s">
         <v>716</v>
@@ -12244,16 +12247,16 @@
       </c>
       <c r="E74" s="7"/>
       <c r="H74" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I74" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I74" s="60" t="s">
+      <c r="J74" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J74" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K74" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L74" s="5" t="s">
         <v>243</v>
@@ -12358,7 +12361,7 @@
         <v>24</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>38</v>
@@ -12367,16 +12370,16 @@
         <v>714</v>
       </c>
       <c r="H75" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I75" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I75" s="60" t="s">
+      <c r="J75" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J75" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K75" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L75" s="5" t="s">
         <v>307</v>
@@ -12509,16 +12512,16 @@
       </c>
       <c r="E76" s="7"/>
       <c r="H76" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I76" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I76" s="60" t="s">
+      <c r="J76" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J76" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K76" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L76" s="5" t="s">
         <v>182</v>
@@ -12626,16 +12629,16 @@
         <v>24</v>
       </c>
       <c r="H77" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I77" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I77" s="60" t="s">
+      <c r="J77" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J77" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K77" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L77" s="5" t="s">
         <v>293</v>
@@ -12756,16 +12759,16 @@
         <v>24</v>
       </c>
       <c r="H78" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I78" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I78" s="60" t="s">
+      <c r="J78" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J78" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K78" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L78" s="5" t="s">
         <v>293</v>
@@ -12893,16 +12896,16 @@
         <v>714</v>
       </c>
       <c r="H79" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I79" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I79" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J79" s="60" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L79" s="5" t="s">
         <v>83</v>
@@ -12997,7 +13000,7 @@
         <v>2006</v>
       </c>
       <c r="BK79" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="80" spans="1:63" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.2">
@@ -13023,16 +13026,16 @@
         <v>714</v>
       </c>
       <c r="H80" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I80" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I80" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J80" s="60" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L80" s="5" t="s">
         <v>83</v>
@@ -13127,7 +13130,7 @@
         <v>2006</v>
       </c>
       <c r="BK80" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="81" spans="1:66" s="2" customFormat="1" ht="14" x14ac:dyDescent="0.2">
@@ -13145,13 +13148,13 @@
       </c>
       <c r="E81" s="7"/>
       <c r="H81" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I81" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I81" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K81" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L81" s="5" t="s">
         <v>157</v>
@@ -13253,13 +13256,13 @@
       </c>
       <c r="E82" s="7"/>
       <c r="H82" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I82" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I82" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K82" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L82" s="5" t="s">
         <v>157</v>
@@ -13365,13 +13368,13 @@
         <v>24</v>
       </c>
       <c r="H83" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I83" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I83" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K83" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L83" s="5" t="s">
         <v>139</v>
@@ -13494,13 +13497,13 @@
         <v>24</v>
       </c>
       <c r="H84" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I84" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I84" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K84" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L84" s="5" t="s">
         <v>139</v>
@@ -13623,13 +13626,13 @@
         <v>24</v>
       </c>
       <c r="H85" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I85" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I85" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K85" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L85" s="5" t="s">
         <v>139</v>
@@ -13752,13 +13755,13 @@
         <v>24</v>
       </c>
       <c r="H86" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I86" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I86" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K86" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L86" s="5" t="s">
         <v>139</v>
@@ -13881,13 +13884,13 @@
         <v>24</v>
       </c>
       <c r="H87" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I87" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I87" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K87" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L87" s="5" t="s">
         <v>139</v>
@@ -14009,14 +14012,14 @@
       </c>
       <c r="G88" s="2"/>
       <c r="H88" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I88" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="J88" s="2"/>
       <c r="K88" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L88" s="5" t="s">
         <v>139</v>
@@ -14148,13 +14151,13 @@
         <v>24</v>
       </c>
       <c r="H89" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I89" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I89" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K89" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L89" s="5" t="s">
         <v>139</v>
@@ -14276,13 +14279,13 @@
         <v>24</v>
       </c>
       <c r="H90" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I90" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I90" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K90" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L90" s="5" t="s">
         <v>139</v>
@@ -14403,13 +14406,13 @@
         <v>24</v>
       </c>
       <c r="H91" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I91" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I91" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K91" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L91" s="5" t="s">
         <v>139</v>
@@ -14530,13 +14533,13 @@
         <v>24</v>
       </c>
       <c r="H92" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I92" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I92" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K92" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L92" s="5" t="s">
         <v>139</v>
@@ -14657,13 +14660,13 @@
         <v>24</v>
       </c>
       <c r="H93" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I93" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I93" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K93" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L93" s="5" t="s">
         <v>139</v>
@@ -14785,14 +14788,14 @@
       </c>
       <c r="G94" s="2"/>
       <c r="H94" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I94" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="J94" s="2"/>
       <c r="K94" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L94" s="5" t="s">
         <v>139</v>
@@ -14919,14 +14922,14 @@
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I95" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="J95" s="2"/>
       <c r="K95" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L95" s="5" t="s">
         <v>371</v>
@@ -15049,14 +15052,14 @@
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I96" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="J96" s="2"/>
       <c r="K96" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L96" s="5" t="s">
         <v>371</v>
@@ -15180,16 +15183,16 @@
         <v>38</v>
       </c>
       <c r="H97" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I97" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I97" s="60" t="s">
+      <c r="J97" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J97" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K97" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L97" s="5" t="s">
         <v>274</v>
@@ -15288,16 +15291,16 @@
         <v>38</v>
       </c>
       <c r="H98" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I98" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I98" s="60" t="s">
+      <c r="J98" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J98" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K98" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L98" s="5" t="s">
         <v>274</v>
@@ -15397,16 +15400,16 @@
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I99" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I99" s="60" t="s">
+      <c r="J99" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J99" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K99" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="L99" s="5" t="s">
         <v>286</v>
@@ -15531,16 +15534,16 @@
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
       <c r="H100" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I100" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I100" s="60" t="s">
+      <c r="J100" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J100" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K100" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L100" s="5" t="s">
         <v>280</v>
@@ -15562,7 +15565,7 @@
         <v>282</v>
       </c>
       <c r="S100" s="5" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="T100" s="5" t="s">
         <v>283</v>
@@ -15666,7 +15669,7 @@
         <v>24</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>38</v>
@@ -15675,16 +15678,16 @@
         <v>714</v>
       </c>
       <c r="H101" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I101" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I101" s="60" t="s">
+      <c r="J101" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J101" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K101" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L101" s="7" t="s">
         <v>307</v>
@@ -15797,16 +15800,16 @@
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
       <c r="H102" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I102" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I102" s="60" t="s">
+      <c r="J102" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J102" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K102" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L102" s="5" t="s">
         <v>427</v>
@@ -15914,7 +15917,7 @@
         <v>2013</v>
       </c>
       <c r="BK102" s="7" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="BL102"/>
       <c r="BM102"/>
@@ -15935,16 +15938,16 @@
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
       <c r="H103" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I103" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I103" s="60" t="s">
+      <c r="J103" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J103" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K103" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L103" s="5" t="s">
         <v>427</v>
@@ -16044,11 +16047,11 @@
         <v>507</v>
       </c>
       <c r="BI103" s="7" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="BJ103" s="7"/>
       <c r="BK103" s="7" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="BL103"/>
       <c r="BM103"/>
@@ -16069,16 +16072,16 @@
       <c r="F104" s="7"/>
       <c r="G104" s="7"/>
       <c r="H104" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I104" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I104" s="60" t="s">
+      <c r="J104" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J104" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K104" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L104" s="5" t="s">
         <v>427</v>
@@ -16188,7 +16191,7 @@
         <v>2013</v>
       </c>
       <c r="BK104" s="7" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="BL104"/>
       <c r="BM104"/>
@@ -16209,16 +16212,16 @@
       <c r="F105" s="7"/>
       <c r="G105" s="7"/>
       <c r="H105" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I105" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I105" s="60" t="s">
+      <c r="J105" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J105" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K105" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L105" s="5" t="s">
         <v>427</v>
@@ -16243,7 +16246,7 @@
         <v>702</v>
       </c>
       <c r="T105" s="35" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="U105" s="35" t="s">
         <v>17</v>
@@ -16328,7 +16331,7 @@
         <v>2013</v>
       </c>
       <c r="BK105" s="7" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="BL105"/>
       <c r="BM105"/>
@@ -16349,16 +16352,16 @@
       <c r="F106" s="7"/>
       <c r="G106" s="7"/>
       <c r="H106" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I106" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I106" s="60" t="s">
+      <c r="J106" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J106" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K106" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L106" s="5" t="s">
         <v>427</v>
@@ -16383,7 +16386,7 @@
         <v>702</v>
       </c>
       <c r="T106" s="35" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="U106" s="35" t="s">
         <v>17</v>
@@ -16466,7 +16469,7 @@
         <v>2013</v>
       </c>
       <c r="BK106" s="7" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="BL106"/>
       <c r="BM106"/>
@@ -16484,23 +16487,23 @@
         <v>24</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F107" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I107" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I107" s="60" t="s">
+      <c r="J107" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J107" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K107" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L107" s="5" t="s">
         <v>417</v>
@@ -16628,23 +16631,23 @@
         <v>24</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F108" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I108" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I108" s="60" t="s">
+      <c r="J108" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J108" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K108" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L108" s="5" t="s">
         <v>417</v>
@@ -16772,23 +16775,23 @@
         <v>24</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F109" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I109" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I109" s="60" t="s">
+      <c r="J109" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J109" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K109" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L109" s="5" t="s">
         <v>417</v>
@@ -16910,23 +16913,23 @@
         <v>24</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F110" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G110" s="7"/>
       <c r="H110" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I110" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I110" s="60" t="s">
+      <c r="J110" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J110" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K110" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L110" s="5" t="s">
         <v>417</v>
@@ -17056,23 +17059,23 @@
         <v>24</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I111" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I111" s="60" t="s">
+      <c r="J111" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J111" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K111" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L111" s="5" t="s">
         <v>417</v>
@@ -17200,23 +17203,23 @@
         <v>24</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="F112" s="7" t="s">
         <v>24</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I112" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I112" s="60" t="s">
+      <c r="J112" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J112" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K112" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L112" s="5" t="s">
         <v>417</v>
@@ -17348,13 +17351,13 @@
         <v>714</v>
       </c>
       <c r="H113" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I113" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I113" s="2" t="s">
+      <c r="K113" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="K113" s="2" t="s">
-        <v>790</v>
       </c>
       <c r="L113" s="5" t="s">
         <v>371</v>
@@ -17457,19 +17460,19 @@
         <v>24</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H114" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I114" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I114" s="2" t="s">
+      <c r="K114" s="2" t="s">
         <v>789</v>
-      </c>
-      <c r="K114" s="2" t="s">
-        <v>790</v>
       </c>
       <c r="L114" s="5" t="s">
         <v>371</v>
@@ -17570,16 +17573,16 @@
       <c r="F115" s="7"/>
       <c r="G115" s="7"/>
       <c r="H115" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I115" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I115" s="60" t="s">
+      <c r="J115" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J115" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K115" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L115" s="5" t="s">
         <v>430</v>
@@ -17696,16 +17699,16 @@
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
       <c r="H116" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I116" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I116" s="60" t="s">
+      <c r="J116" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J116" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K116" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L116" s="5" t="s">
         <v>430</v>
@@ -17822,16 +17825,16 @@
       <c r="F117" s="7"/>
       <c r="G117" s="7"/>
       <c r="H117" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I117" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I117" s="60" t="s">
+      <c r="J117" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J117" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K117" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L117" s="5" t="s">
         <v>430</v>
@@ -17950,16 +17953,16 @@
       <c r="F118" s="7"/>
       <c r="G118" s="7"/>
       <c r="H118" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I118" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I118" s="60" t="s">
+      <c r="J118" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J118" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K118" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L118" s="5" t="s">
         <v>430</v>
@@ -18082,16 +18085,16 @@
       <c r="F119" s="7"/>
       <c r="G119" s="7"/>
       <c r="H119" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I119" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I119" s="60" t="s">
+      <c r="J119" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J119" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K119" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L119" s="7" t="s">
         <v>182</v>
@@ -18218,16 +18221,16 @@
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
       <c r="H120" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I120" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I120" s="60" t="s">
+      <c r="J120" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J120" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K120" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L120" s="7" t="s">
         <v>182</v>
@@ -18354,16 +18357,16 @@
       <c r="F121" s="7"/>
       <c r="G121" s="7"/>
       <c r="H121" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I121" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I121" s="60" t="s">
+      <c r="J121" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J121" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K121" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L121" s="7" t="s">
         <v>182</v>
@@ -18488,16 +18491,16 @@
       <c r="F122" s="7"/>
       <c r="G122" s="7"/>
       <c r="H122" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I122" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I122" s="60" t="s">
+      <c r="J122" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J122" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K122" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L122" s="7" t="s">
         <v>182</v>
@@ -18626,16 +18629,16 @@
       <c r="F123" s="7"/>
       <c r="G123" s="7"/>
       <c r="H123" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I123" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I123" s="60" t="s">
+      <c r="J123" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J123" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K123" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L123" s="5" t="s">
         <v>418</v>
@@ -18760,16 +18763,16 @@
       <c r="F124" s="7"/>
       <c r="G124" s="7"/>
       <c r="H124" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I124" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I124" s="60" t="s">
+      <c r="J124" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J124" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K124" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L124" s="5" t="s">
         <v>418</v>
@@ -18898,16 +18901,16 @@
       <c r="F125" s="7"/>
       <c r="G125" s="7"/>
       <c r="H125" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I125" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I125" s="60" t="s">
+      <c r="J125" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J125" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K125" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L125" s="7" t="s">
         <v>114</v>
@@ -19029,16 +19032,16 @@
         <v>727</v>
       </c>
       <c r="H126" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I126" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I126" s="60" t="s">
+      <c r="J126" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J126" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K126" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L126" s="16" t="s">
         <v>114</v>
@@ -19167,16 +19170,16 @@
         <v>727</v>
       </c>
       <c r="H127" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I127" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I127" s="60" t="s">
+      <c r="J127" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J127" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K127" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L127" s="16" t="s">
         <v>114</v>
@@ -19305,16 +19308,16 @@
         <v>727</v>
       </c>
       <c r="H128" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I128" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I128" s="60" t="s">
+      <c r="J128" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J128" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K128" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L128" s="16" t="s">
         <v>114</v>
@@ -19444,16 +19447,16 @@
         <v>714</v>
       </c>
       <c r="H129" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I129" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I129" s="60" t="s">
+      <c r="J129" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J129" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K129" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L129" s="5" t="s">
         <v>352</v>
@@ -19567,16 +19570,16 @@
         <v>24</v>
       </c>
       <c r="H130" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I130" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I130" s="60" t="s">
+      <c r="J130" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J130" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K130" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L130" s="5" t="s">
         <v>352</v>
@@ -19695,16 +19698,16 @@
       <c r="F131" s="7"/>
       <c r="G131" s="7"/>
       <c r="H131" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I131" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I131" s="60" t="s">
+      <c r="J131" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J131" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K131" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L131" s="7" t="s">
         <v>293</v>
@@ -19831,16 +19834,16 @@
       <c r="F132" s="7"/>
       <c r="G132" s="7"/>
       <c r="H132" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I132" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I132" s="60" t="s">
+      <c r="J132" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J132" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K132" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L132" s="7" t="s">
         <v>293</v>
@@ -19961,16 +19964,16 @@
       <c r="F133" s="7"/>
       <c r="G133" s="7"/>
       <c r="H133" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I133" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I133" s="60" t="s">
+      <c r="J133" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J133" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K133" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L133" s="7" t="s">
         <v>293</v>
@@ -20099,16 +20102,16 @@
       <c r="F134" s="7"/>
       <c r="G134" s="7"/>
       <c r="H134" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I134" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I134" s="60" t="s">
+      <c r="J134" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J134" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K134" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L134" s="7" t="s">
         <v>293</v>
@@ -20227,7 +20230,7 @@
         <v>24</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F135" s="11" t="s">
         <v>38</v>
@@ -20236,16 +20239,16 @@
         <v>714</v>
       </c>
       <c r="H135" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I135" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I135" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J135" s="60" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K135" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L135" s="12" t="s">
         <v>83</v>
@@ -20369,7 +20372,7 @@
         <v>2010</v>
       </c>
       <c r="BK135" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="BL135" s="11"/>
       <c r="BM135" s="11"/>
@@ -20389,7 +20392,7 @@
         <v>24</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F136" s="11" t="s">
         <v>38</v>
@@ -20398,16 +20401,16 @@
         <v>714</v>
       </c>
       <c r="H136" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I136" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I136" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J136" s="60" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K136" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L136" s="12" t="s">
         <v>83</v>
@@ -20531,7 +20534,7 @@
         <v>2010</v>
       </c>
       <c r="BK136" s="11" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="BL136" s="11"/>
       <c r="BM136" s="11"/>
@@ -20551,7 +20554,7 @@
         <v>24</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F137" s="11" t="s">
         <v>38</v>
@@ -20560,16 +20563,16 @@
         <v>714</v>
       </c>
       <c r="H137" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I137" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I137" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J137" s="60" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L137" s="12" t="s">
         <v>83</v>
@@ -20693,7 +20696,7 @@
         <v>2010</v>
       </c>
       <c r="BK137" s="11" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="BL137" s="11"/>
       <c r="BM137" s="11"/>
@@ -20710,22 +20713,22 @@
         <v>24</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H138" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I138" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I138" s="60" t="s">
+      <c r="J138" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J138" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K138" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L138" s="5" t="s">
         <v>307</v>
@@ -20846,13 +20849,13 @@
         <v>712</v>
       </c>
       <c r="H139" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I139" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I139" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K139" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L139" s="5" t="s">
         <v>194</v>
@@ -20947,13 +20950,13 @@
         <v>712</v>
       </c>
       <c r="H140" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I140" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I140" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K140" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L140" s="5" t="s">
         <v>194</v>
@@ -21048,13 +21051,13 @@
         <v>712</v>
       </c>
       <c r="H141" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I141" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I141" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K141" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L141" s="5" t="s">
         <v>194</v>
@@ -21149,13 +21152,13 @@
         <v>712</v>
       </c>
       <c r="H142" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I142" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I142" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K142" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L142" s="5" t="s">
         <v>194</v>
@@ -21250,13 +21253,13 @@
         <v>712</v>
       </c>
       <c r="H143" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I143" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I143" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K143" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L143" s="5" t="s">
         <v>194</v>
@@ -21351,13 +21354,13 @@
         <v>712</v>
       </c>
       <c r="H144" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I144" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I144" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K144" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L144" s="5" t="s">
         <v>194</v>
@@ -21452,13 +21455,13 @@
         <v>712</v>
       </c>
       <c r="H145" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I145" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I145" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K145" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L145" s="5" t="s">
         <v>194</v>
@@ -21553,13 +21556,13 @@
         <v>712</v>
       </c>
       <c r="H146" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I146" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I146" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K146" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L146" s="5" t="s">
         <v>194</v>
@@ -21654,13 +21657,13 @@
         <v>712</v>
       </c>
       <c r="H147" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I147" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I147" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K147" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L147" s="5" t="s">
         <v>194</v>
@@ -21755,13 +21758,13 @@
         <v>712</v>
       </c>
       <c r="H148" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I148" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I148" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K148" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L148" s="5" t="s">
         <v>194</v>
@@ -21856,13 +21859,13 @@
         <v>712</v>
       </c>
       <c r="H149" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I149" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I149" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K149" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L149" s="5" t="s">
         <v>194</v>
@@ -21960,13 +21963,13 @@
         <v>712</v>
       </c>
       <c r="H150" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I150" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I150" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K150" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L150" s="5" t="s">
         <v>194</v>
@@ -22061,13 +22064,13 @@
         <v>712</v>
       </c>
       <c r="H151" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I151" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I151" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K151" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L151" s="5" t="s">
         <v>194</v>
@@ -22162,13 +22165,13 @@
         <v>712</v>
       </c>
       <c r="H152" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I152" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I152" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K152" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L152" s="5" t="s">
         <v>194</v>
@@ -22263,13 +22266,13 @@
         <v>712</v>
       </c>
       <c r="H153" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I153" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I153" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K153" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L153" s="5" t="s">
         <v>194</v>
@@ -22364,13 +22367,13 @@
         <v>712</v>
       </c>
       <c r="H154" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I154" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I154" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K154" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L154" s="5" t="s">
         <v>194</v>
@@ -22466,16 +22469,16 @@
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
       <c r="H155" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I155" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I155" s="60" t="s">
+      <c r="J155" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J155" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K155" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L155" s="5" t="s">
         <v>161</v>
@@ -22608,16 +22611,16 @@
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
       <c r="H156" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I156" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I156" s="60" t="s">
+      <c r="J156" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J156" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K156" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L156" s="5" t="s">
         <v>161</v>
@@ -22750,16 +22753,16 @@
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
       <c r="H157" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I157" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I157" s="60" t="s">
+      <c r="J157" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J157" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K157" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L157" s="5" t="s">
         <v>465</v>
@@ -22884,16 +22887,16 @@
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
       <c r="H158" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I158" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I158" s="60" t="s">
+      <c r="J158" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J158" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K158" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="L158" s="5" t="s">
         <v>205</v>
@@ -23021,16 +23024,16 @@
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
       <c r="H159" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I159" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I159" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J159" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K159" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L159" s="2" t="s">
         <v>8</v>
@@ -23171,16 +23174,16 @@
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
       <c r="H160" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I160" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I160" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J160" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L160" s="2" t="s">
         <v>8</v>
@@ -23313,16 +23316,16 @@
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
       <c r="H161" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I161" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I161" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J161" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K161" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L161" s="2" t="s">
         <v>8</v>
@@ -23455,16 +23458,16 @@
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
       <c r="H162" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I162" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I162" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J162" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K162" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L162" s="2" t="s">
         <v>8</v>
@@ -23603,13 +23606,13 @@
       </c>
       <c r="E163" s="7"/>
       <c r="H163" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I163" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I163" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K163" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L163" s="5" t="s">
         <v>214</v>
@@ -23731,13 +23734,13 @@
       </c>
       <c r="E164" s="7"/>
       <c r="H164" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I164" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I164" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K164" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L164" s="5" t="s">
         <v>214</v>
@@ -23859,13 +23862,13 @@
       </c>
       <c r="E165" s="7"/>
       <c r="H165" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I165" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I165" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K165" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L165" s="5" t="s">
         <v>214</v>
@@ -23962,13 +23965,13 @@
       </c>
       <c r="E166" s="7"/>
       <c r="H166" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I166" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I166" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K166" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L166" s="5" t="s">
         <v>214</v>
@@ -24090,13 +24093,13 @@
       </c>
       <c r="E167" s="7"/>
       <c r="H167" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I167" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I167" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K167" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L167" s="5" t="s">
         <v>214</v>
@@ -24192,13 +24195,13 @@
       </c>
       <c r="E168" s="7"/>
       <c r="H168" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I168" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I168" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K168" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L168" s="5" t="s">
         <v>214</v>
@@ -24294,13 +24297,13 @@
       </c>
       <c r="E169" s="7"/>
       <c r="H169" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I169" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I169" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K169" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L169" s="5" t="s">
         <v>214</v>
@@ -24415,13 +24418,13 @@
       </c>
       <c r="E170" s="7"/>
       <c r="H170" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I170" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I170" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K170" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L170" s="5" t="s">
         <v>214</v>
@@ -24533,13 +24536,13 @@
       </c>
       <c r="E171" s="7"/>
       <c r="H171" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I171" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I171" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K171" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L171" s="5" t="s">
         <v>214</v>
@@ -24658,14 +24661,14 @@
       <c r="F172" s="7"/>
       <c r="G172" s="7"/>
       <c r="H172" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I172" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="I172" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="J172" s="7"/>
       <c r="K172" s="7" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="L172" s="7" t="s">
         <v>664</v>
@@ -24776,16 +24779,16 @@
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
       <c r="H173" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I173" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I173" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J173" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K173" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L173" s="7" t="s">
         <v>42</v>
@@ -24913,16 +24916,16 @@
         <v>38</v>
       </c>
       <c r="H174" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I174" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I174" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J174" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K174" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L174" s="7" t="s">
         <v>42</v>
@@ -25025,16 +25028,16 @@
         <v>38</v>
       </c>
       <c r="H175" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I175" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I175" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J175" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K175" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L175" s="7" t="s">
         <v>42</v>
@@ -25137,16 +25140,16 @@
         <v>38</v>
       </c>
       <c r="H176" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I176" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I176" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J176" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K176" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L176" s="7" t="s">
         <v>42</v>
@@ -25249,16 +25252,16 @@
         <v>38</v>
       </c>
       <c r="H177" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I177" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I177" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J177" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K177" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L177" s="7" t="s">
         <v>42</v>
@@ -25364,16 +25367,16 @@
         <v>38</v>
       </c>
       <c r="H178" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I178" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I178" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J178" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K178" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L178" s="7" t="s">
         <v>42</v>
@@ -25479,16 +25482,16 @@
         <v>38</v>
       </c>
       <c r="H179" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I179" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I179" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J179" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K179" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L179" s="7" t="s">
         <v>42</v>
@@ -25594,16 +25597,16 @@
         <v>38</v>
       </c>
       <c r="H180" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I180" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I180" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J180" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K180" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L180" s="7" t="s">
         <v>42</v>
@@ -25715,16 +25718,16 @@
         <v>38</v>
       </c>
       <c r="H181" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I181" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I181" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J181" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K181" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L181" s="7" t="s">
         <v>42</v>
@@ -25827,16 +25830,16 @@
         <v>38</v>
       </c>
       <c r="H182" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I182" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I182" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J182" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K182" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L182" s="7" t="s">
         <v>42</v>
@@ -25939,16 +25942,16 @@
         <v>38</v>
       </c>
       <c r="H183" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I183" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I183" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J183" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K183" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L183" s="7" t="s">
         <v>42</v>
@@ -26055,7 +26058,7 @@
         <v>24</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="F184" s="7" t="s">
         <v>38</v>
@@ -26064,16 +26067,16 @@
         <v>714</v>
       </c>
       <c r="H184" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I184" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I184" s="60" t="s">
+      <c r="J184" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J184" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K184" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L184" s="7" t="s">
         <v>378</v>
@@ -26095,10 +26098,10 @@
         <v>263</v>
       </c>
       <c r="S184" s="7" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="T184" s="7" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="U184" s="7" t="s">
         <v>48</v>
@@ -26200,16 +26203,16 @@
       <c r="F185" s="7"/>
       <c r="G185" s="7"/>
       <c r="H185" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I185" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I185" s="60" t="s">
+      <c r="J185" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J185" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K185" s="7" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L185" s="5" t="s">
         <v>100</v>
@@ -26328,16 +26331,16 @@
         <v>714</v>
       </c>
       <c r="H186" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I186" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I186" s="60" t="s">
+      <c r="J186" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J186" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K186" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L186" s="7" t="s">
         <v>161</v>
@@ -26476,16 +26479,16 @@
         <v>714</v>
       </c>
       <c r="H187" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I187" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I187" s="60" t="s">
+      <c r="J187" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J187" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K187" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L187" s="7" t="s">
         <v>161</v>
@@ -26612,13 +26615,13 @@
         <v>38</v>
       </c>
       <c r="H188" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I188" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I188" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K188" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L188" s="5" t="s">
         <v>364</v>
@@ -26730,13 +26733,13 @@
         <v>24</v>
       </c>
       <c r="H189" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I189" s="2" t="s">
         <v>788</v>
       </c>
-      <c r="I189" s="2" t="s">
-        <v>789</v>
-      </c>
       <c r="K189" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L189" s="7" t="s">
         <v>107</v>
@@ -26833,13 +26836,13 @@
         <v>507</v>
       </c>
       <c r="BI189" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="BJ189" s="2">
         <v>2007</v>
       </c>
       <c r="BK189" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="BL189" s="2"/>
       <c r="BM189" s="2"/>
@@ -26860,16 +26863,16 @@
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I190" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I190" s="60" t="s">
+      <c r="J190" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J190" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K190" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L190" s="5" t="s">
         <v>327</v>
@@ -26981,16 +26984,16 @@
       <c r="F191" s="60"/>
       <c r="G191" s="60"/>
       <c r="H191" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I191" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I191" s="60" t="s">
+      <c r="J191" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J191" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K191" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L191" s="35" t="s">
         <v>327</v>
@@ -27103,16 +27106,16 @@
       <c r="F192" s="60"/>
       <c r="G192" s="60"/>
       <c r="H192" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I192" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I192" s="60" t="s">
+      <c r="J192" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J192" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K192" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L192" s="35" t="s">
         <v>327</v>
@@ -27221,16 +27224,16 @@
         <v>38</v>
       </c>
       <c r="H193" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I193" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I193" s="60" t="s">
+      <c r="J193" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J193" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K193" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L193" s="5" t="s">
         <v>418</v>
@@ -27335,16 +27338,16 @@
         <v>38</v>
       </c>
       <c r="H194" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I194" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I194" s="60" t="s">
+      <c r="J194" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J194" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K194" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L194" s="5" t="s">
         <v>418</v>
@@ -27458,16 +27461,16 @@
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
       <c r="H195" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I195" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I195" s="60" t="s">
+      <c r="J195" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J195" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K195" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L195" s="5" t="s">
         <v>243</v>
@@ -27608,16 +27611,16 @@
         <v>714</v>
       </c>
       <c r="H196" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I196" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I196" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J196" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K196" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L196" s="5" t="s">
         <v>70</v>
@@ -27754,16 +27757,16 @@
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
       <c r="H197" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I197" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I197" s="60" t="s">
+      <c r="J197" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J197" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K197" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L197" s="5" t="s">
         <v>228</v>
@@ -27895,16 +27898,16 @@
         <v>714</v>
       </c>
       <c r="H198" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I198" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I198" s="60" t="s">
+      <c r="J198" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J198" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K198" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L198" s="5" t="s">
         <v>293</v>
@@ -28037,16 +28040,16 @@
         <v>714</v>
       </c>
       <c r="H199" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I199" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I199" s="60" t="s">
+      <c r="J199" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J199" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K199" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L199" s="5" t="s">
         <v>293</v>
@@ -28178,7 +28181,7 @@
         <v>24</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>38</v>
@@ -28187,16 +28190,16 @@
         <v>727</v>
       </c>
       <c r="H200" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I200" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I200" s="60" t="s">
+      <c r="J200" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J200" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K200" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L200" s="5" t="s">
         <v>307</v>
@@ -28300,7 +28303,7 @@
         <v>2017</v>
       </c>
       <c r="BK200" s="7" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="BL200" s="2"/>
       <c r="BM200" s="2"/>
@@ -28322,16 +28325,16 @@
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I201" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I201" s="60" t="s">
+      <c r="J201" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J201" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K201" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L201" s="5" t="s">
         <v>124</v>
@@ -28438,16 +28441,16 @@
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I202" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I202" s="60" t="s">
+      <c r="J202" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J202" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K202" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L202" s="5" t="s">
         <v>256</v>
@@ -28577,16 +28580,16 @@
         <v>38</v>
       </c>
       <c r="H203" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I203" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I203" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J203" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K203" s="7" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L203" s="5" t="s">
         <v>77</v>
@@ -28704,16 +28707,16 @@
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
       <c r="H204" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I204" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I204" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J204" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K204" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="L204" s="5" t="s">
         <v>368</v>
@@ -28832,16 +28835,16 @@
       </c>
       <c r="G205" s="2"/>
       <c r="H205" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I205" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I205" s="60" t="s">
+      <c r="J205" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J205" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K205" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L205" s="5" t="s">
         <v>161</v>
@@ -28972,16 +28975,16 @@
       </c>
       <c r="G206" s="2"/>
       <c r="H206" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I206" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I206" s="60" t="s">
+      <c r="J206" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J206" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K206" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L206" s="5" t="s">
         <v>161</v>
@@ -29116,16 +29119,16 @@
       </c>
       <c r="G207" s="2"/>
       <c r="H207" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I207" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I207" s="60" t="s">
+      <c r="J207" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J207" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K207" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L207" s="5" t="s">
         <v>161</v>
@@ -29252,16 +29255,16 @@
       </c>
       <c r="G208" s="2"/>
       <c r="H208" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I208" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I208" s="60" t="s">
+      <c r="J208" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J208" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K208" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L208" s="5" t="s">
         <v>161</v>
@@ -29392,16 +29395,16 @@
       </c>
       <c r="G209" s="2"/>
       <c r="H209" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I209" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I209" s="60" t="s">
+      <c r="J209" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J209" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K209" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L209" s="5" t="s">
         <v>161</v>
@@ -29532,16 +29535,16 @@
       </c>
       <c r="G210" s="2"/>
       <c r="H210" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I210" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I210" s="60" t="s">
+      <c r="J210" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J210" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K210" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L210" s="5" t="s">
         <v>161</v>
@@ -29676,16 +29679,16 @@
       </c>
       <c r="G211" s="2"/>
       <c r="H211" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I211" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I211" s="60" t="s">
+      <c r="J211" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J211" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K211" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L211" s="5" t="s">
         <v>161</v>
@@ -29818,16 +29821,16 @@
       </c>
       <c r="G212" s="2"/>
       <c r="H212" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I212" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I212" s="60" t="s">
+      <c r="J212" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J212" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K212" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L212" s="5" t="s">
         <v>161</v>
@@ -29950,16 +29953,16 @@
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
       <c r="H213" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I213" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I213" s="60" t="s">
+      <c r="J213" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J213" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K213" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L213" s="5" t="s">
         <v>260</v>
@@ -30088,16 +30091,16 @@
         <v>714</v>
       </c>
       <c r="H214" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I214" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I214" s="60" t="s">
+      <c r="J214" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J214" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K214" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L214" s="7" t="s">
         <v>307</v>
@@ -30210,16 +30213,16 @@
         <v>24</v>
       </c>
       <c r="H215" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I215" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I215" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J215" s="60" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K215" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L215" s="5" t="s">
         <v>83</v>
@@ -30353,16 +30356,16 @@
         <v>24</v>
       </c>
       <c r="H216" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I216" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I216" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J216" s="60" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K216" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="L216" s="5" t="s">
         <v>83</v>
@@ -30497,14 +30500,14 @@
         <v>714</v>
       </c>
       <c r="H217" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I217" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="I217" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="J217" s="2"/>
       <c r="K217" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L217" s="12" t="s">
         <v>139</v>
@@ -30631,14 +30634,14 @@
         <v>714</v>
       </c>
       <c r="H218" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I218" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="I218" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="J218" s="2"/>
       <c r="K218" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L218" s="12" t="s">
         <v>139</v>
@@ -30767,14 +30770,14 @@
         <v>714</v>
       </c>
       <c r="H219" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I219" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="I219" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="J219" s="2"/>
       <c r="K219" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L219" s="12" t="s">
         <v>139</v>
@@ -30901,14 +30904,14 @@
         <v>714</v>
       </c>
       <c r="H220" s="2" t="s">
+        <v>787</v>
+      </c>
+      <c r="I220" s="2" t="s">
         <v>788</v>
-      </c>
-      <c r="I220" s="2" t="s">
-        <v>789</v>
       </c>
       <c r="J220" s="2"/>
       <c r="K220" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="L220" s="12" t="s">
         <v>139</v>
@@ -31033,16 +31036,16 @@
         <v>714</v>
       </c>
       <c r="H221" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I221" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I221" s="60" t="s">
+      <c r="J221" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J221" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K221" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L221" s="5" t="s">
         <v>307</v>
@@ -31158,7 +31161,7 @@
         <v>2009</v>
       </c>
       <c r="BK221" s="5" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="BL221" s="2"/>
       <c r="BM221" s="2"/>
@@ -31179,16 +31182,16 @@
       <c r="F222" s="11"/>
       <c r="G222" s="11"/>
       <c r="H222" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I222" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I222" s="60" t="s">
+      <c r="J222" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J222" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K222" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L222" s="11" t="s">
         <v>378</v>
@@ -31210,7 +31213,7 @@
         <v>263</v>
       </c>
       <c r="S222" s="5" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="T222" s="12" t="s">
         <v>644</v>
@@ -31292,7 +31295,7 @@
         <v>2014</v>
       </c>
       <c r="BK222" s="11" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="BL222" s="11"/>
       <c r="BM222" s="11"/>
@@ -31313,16 +31316,16 @@
       <c r="F223" s="60"/>
       <c r="G223" s="60"/>
       <c r="H223" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I223" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I223" s="60" t="s">
+      <c r="J223" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J223" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K223" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L223" s="35" t="s">
         <v>341</v>
@@ -31344,7 +31347,7 @@
         <v>344</v>
       </c>
       <c r="S223" s="60" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="T223" s="60" t="s">
         <v>642</v>
@@ -31441,16 +31444,16 @@
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
       <c r="H224" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I224" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I224" s="60" t="s">
+      <c r="J224" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J224" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K224" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L224" s="2" t="s">
         <v>378</v>
@@ -31472,7 +31475,7 @@
         <v>263</v>
       </c>
       <c r="S224" s="5" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="T224" s="5" t="s">
         <v>644</v>
@@ -31552,7 +31555,7 @@
         <v>2014</v>
       </c>
       <c r="BK224" s="11" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="BL224" s="2"/>
       <c r="BM224" s="2"/>
@@ -31569,13 +31572,13 @@
         <v>38</v>
       </c>
       <c r="H225" s="60" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="I225" s="7" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="K225" s="7" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="L225" s="7" t="s">
         <v>553</v>
@@ -31680,16 +31683,16 @@
         <v>714</v>
       </c>
       <c r="H226" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I226" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I226" s="60" t="s">
+      <c r="J226" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J226" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K226" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L226" s="7" t="s">
         <v>307</v>
@@ -31791,7 +31794,7 @@
         <v>2020</v>
       </c>
       <c r="BK226" s="7" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="227" spans="2:63" x14ac:dyDescent="0.2">
@@ -31812,16 +31815,16 @@
       </c>
       <c r="G227" s="2"/>
       <c r="H227" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I227" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I227" s="60" t="s">
+      <c r="J227" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J227" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K227" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L227" s="7" t="s">
         <v>293</v>
@@ -31926,16 +31929,16 @@
         <v>24</v>
       </c>
       <c r="H228" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I228" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I228" s="60" t="s">
+      <c r="J228" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J228" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K228" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L228" s="7" t="s">
         <v>293</v>
@@ -32042,13 +32045,13 @@
         <v>38</v>
       </c>
       <c r="H229" s="60" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="I229" s="7" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="K229" s="7" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="L229" s="7" t="s">
         <v>553</v>
@@ -32150,13 +32153,13 @@
         <v>38</v>
       </c>
       <c r="H230" s="60" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="I230" s="7" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="K230" s="7" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="L230" s="7" t="s">
         <v>553</v>
@@ -32264,16 +32267,16 @@
         <v>24</v>
       </c>
       <c r="H231" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I231" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I231" s="60" t="s">
-        <v>784</v>
-      </c>
       <c r="J231" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K231" s="7" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="L231" s="7" t="s">
         <v>70</v>
@@ -32420,16 +32423,16 @@
         <v>24</v>
       </c>
       <c r="H232" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I232" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I232" s="60" t="s">
+      <c r="J232" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J232" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K232" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L232" s="7" t="s">
         <v>307</v>
@@ -32553,16 +32556,16 @@
         <v>714</v>
       </c>
       <c r="H233" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I233" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I233" s="60" t="s">
+      <c r="J233" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J233" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K233" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L233" s="7" t="s">
         <v>307</v>
@@ -32665,16 +32668,16 @@
         <v>24</v>
       </c>
       <c r="H234" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I234" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I234" s="60" t="s">
+      <c r="J234" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J234" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K234" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L234" s="7" t="s">
         <v>307</v>
@@ -32775,7 +32778,7 @@
         <v>24</v>
       </c>
       <c r="E235" s="7" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F235" s="7" t="s">
         <v>38</v>
@@ -32784,16 +32787,16 @@
         <v>714</v>
       </c>
       <c r="H235" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I235" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I235" s="60" t="s">
+      <c r="J235" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J235" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K235" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L235" s="7" t="s">
         <v>307</v>
@@ -32889,7 +32892,7 @@
         <v>2023</v>
       </c>
       <c r="BK235" s="7" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
     </row>
     <row r="236" spans="2:63" x14ac:dyDescent="0.2">
@@ -32903,7 +32906,7 @@
         <v>24</v>
       </c>
       <c r="E236" s="7" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="F236" s="7" t="s">
         <v>38</v>
@@ -32912,16 +32915,16 @@
         <v>714</v>
       </c>
       <c r="H236" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I236" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I236" s="60" t="s">
+      <c r="J236" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J236" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K236" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L236" s="7" t="s">
         <v>307</v>
@@ -33017,7 +33020,7 @@
         <v>2017</v>
       </c>
       <c r="BK236" s="7" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="237" spans="2:63" x14ac:dyDescent="0.2">
@@ -33031,22 +33034,22 @@
         <v>24</v>
       </c>
       <c r="E237" s="7" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="F237" s="7" t="s">
         <v>24</v>
       </c>
       <c r="H237" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I237" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I237" s="60" t="s">
+      <c r="J237" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J237" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K237" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L237" s="7" t="s">
         <v>307</v>
@@ -33127,7 +33130,7 @@
         <v>2023</v>
       </c>
       <c r="BK237" s="7" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="238" spans="2:63" x14ac:dyDescent="0.2">
@@ -33141,22 +33144,22 @@
         <v>24</v>
       </c>
       <c r="E238" s="7" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="F238" s="7" t="s">
         <v>24</v>
       </c>
       <c r="H238" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I238" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I238" s="60" t="s">
+      <c r="J238" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J238" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K238" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L238" s="7" t="s">
         <v>307</v>
@@ -33284,7 +33287,7 @@
         <v>24</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F239" s="7" t="s">
         <v>38</v>
@@ -33293,16 +33296,16 @@
         <v>714</v>
       </c>
       <c r="H239" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I239" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I239" s="60" t="s">
+      <c r="J239" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J239" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K239" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L239" s="7" t="s">
         <v>307</v>
@@ -33425,7 +33428,7 @@
         <v>2023</v>
       </c>
       <c r="BK239" s="7" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="240" spans="2:63" x14ac:dyDescent="0.2">
@@ -33439,7 +33442,7 @@
         <v>24</v>
       </c>
       <c r="E240" s="7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F240" s="7" t="s">
         <v>38</v>
@@ -33448,16 +33451,16 @@
         <v>714</v>
       </c>
       <c r="H240" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I240" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I240" s="60" t="s">
+      <c r="J240" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J240" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K240" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L240" s="7" t="s">
         <v>307</v>
@@ -33556,7 +33559,7 @@
         <v>2017</v>
       </c>
       <c r="BK240" s="7" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="241" spans="2:63" x14ac:dyDescent="0.2">
@@ -33570,7 +33573,7 @@
         <v>24</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F241" s="7" t="s">
         <v>38</v>
@@ -33579,16 +33582,16 @@
         <v>714</v>
       </c>
       <c r="H241" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I241" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I241" s="60" t="s">
+      <c r="J241" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J241" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K241" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L241" s="7" t="s">
         <v>307</v>
@@ -33684,7 +33687,7 @@
         <v>2017</v>
       </c>
       <c r="BK241" s="7" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="242" spans="2:63" x14ac:dyDescent="0.2">
@@ -33698,7 +33701,7 @@
         <v>24</v>
       </c>
       <c r="E242" s="7" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F242" s="7" t="s">
         <v>38</v>
@@ -33707,16 +33710,16 @@
         <v>714</v>
       </c>
       <c r="H242" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I242" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I242" s="60" t="s">
+      <c r="J242" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J242" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K242" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L242" s="7" t="s">
         <v>307</v>
@@ -33815,7 +33818,7 @@
         <v>2023</v>
       </c>
       <c r="BK242" s="7" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="243" spans="2:63" x14ac:dyDescent="0.2">
@@ -33829,7 +33832,7 @@
         <v>24</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F243" s="7" t="s">
         <v>38</v>
@@ -33838,16 +33841,16 @@
         <v>714</v>
       </c>
       <c r="H243" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I243" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I243" s="60" t="s">
+      <c r="J243" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J243" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K243" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L243" s="7" t="s">
         <v>307</v>
@@ -33943,7 +33946,7 @@
         <v>2023</v>
       </c>
       <c r="BK243" s="7" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="244" spans="2:63" x14ac:dyDescent="0.2">
@@ -33957,7 +33960,7 @@
         <v>24</v>
       </c>
       <c r="E244" s="7" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="F244" s="7" t="s">
         <v>38</v>
@@ -33966,16 +33969,16 @@
         <v>714</v>
       </c>
       <c r="H244" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I244" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I244" s="60" t="s">
+      <c r="J244" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J244" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K244" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L244" s="7" t="s">
         <v>307</v>
@@ -34077,7 +34080,7 @@
         <v>2001</v>
       </c>
       <c r="BK244" s="7" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="245" spans="2:63" x14ac:dyDescent="0.2">
@@ -34100,16 +34103,16 @@
         <v>714</v>
       </c>
       <c r="H245" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I245" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I245" s="60" t="s">
+      <c r="J245" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J245" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K245" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L245" s="7" t="s">
         <v>307</v>
@@ -34212,7 +34215,7 @@
         <v>2001</v>
       </c>
       <c r="BK245" s="7" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="246" spans="2:63" x14ac:dyDescent="0.2">
@@ -34235,16 +34238,16 @@
         <v>714</v>
       </c>
       <c r="H246" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I246" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I246" s="60" t="s">
+      <c r="J246" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J246" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K246" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L246" s="7" t="s">
         <v>307</v>
@@ -34349,7 +34352,7 @@
         <v>2001</v>
       </c>
       <c r="BK246" s="7" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="247" spans="2:63" x14ac:dyDescent="0.2">
@@ -34369,16 +34372,16 @@
         <v>24</v>
       </c>
       <c r="H247" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I247" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I247" s="60" t="s">
+      <c r="J247" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J247" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K247" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L247" s="7" t="s">
         <v>307</v>
@@ -34483,7 +34486,7 @@
         <v>2023</v>
       </c>
       <c r="BK247" s="7" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="248" spans="2:63" x14ac:dyDescent="0.2">
@@ -34506,16 +34509,16 @@
         <v>714</v>
       </c>
       <c r="H248" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I248" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I248" s="60" t="s">
+      <c r="J248" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J248" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K248" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L248" s="7" t="s">
         <v>307</v>
@@ -34640,16 +34643,16 @@
         <v>714</v>
       </c>
       <c r="H249" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I249" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I249" s="60" t="s">
+      <c r="J249" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J249" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K249" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L249" s="7" t="s">
         <v>307</v>
@@ -34740,16 +34743,16 @@
         <v>714</v>
       </c>
       <c r="H250" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I250" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I250" s="60" t="s">
+      <c r="J250" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J250" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K250" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L250" s="7" t="s">
         <v>307</v>
@@ -34844,16 +34847,16 @@
         <v>714</v>
       </c>
       <c r="H251" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I251" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I251" s="60" t="s">
+      <c r="J251" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J251" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K251" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L251" s="7" t="s">
         <v>307</v>
@@ -34951,16 +34954,16 @@
         <v>714</v>
       </c>
       <c r="H252" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I252" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I252" s="60" t="s">
+      <c r="J252" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J252" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K252" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L252" s="7" t="s">
         <v>307</v>
@@ -35058,16 +35061,16 @@
         <v>714</v>
       </c>
       <c r="H253" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I253" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I253" s="60" t="s">
+      <c r="J253" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J253" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K253" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L253" s="7" t="s">
         <v>293</v>
@@ -35177,16 +35180,16 @@
         <v>714</v>
       </c>
       <c r="H254" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I254" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I254" s="60" t="s">
+      <c r="J254" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J254" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K254" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L254" s="7" t="s">
         <v>293</v>
@@ -35279,7 +35282,7 @@
         <v>2023</v>
       </c>
       <c r="BK254" s="7" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="255" spans="2:63" x14ac:dyDescent="0.2">
@@ -35296,31 +35299,31 @@
         <v>743</v>
       </c>
       <c r="H255" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I255" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I255" s="60" t="s">
+      <c r="J255" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J255" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K255" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L255" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="M255" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="M255" s="7" t="s">
+      <c r="N255" s="7" t="s">
         <v>745</v>
       </c>
-      <c r="N255" s="7" t="s">
+      <c r="O255" s="7" t="s">
         <v>746</v>
       </c>
-      <c r="O255" s="7" t="s">
+      <c r="Q255" s="7" t="s">
         <v>747</v>
-      </c>
-      <c r="Q255" s="7" t="s">
-        <v>748</v>
       </c>
       <c r="R255" s="7" t="s">
         <v>208</v>
@@ -35389,13 +35392,13 @@
         <v>507</v>
       </c>
       <c r="BI255" s="7" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="BJ255" s="7">
         <v>2024</v>
       </c>
       <c r="BK255" s="7" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="256" spans="2:63" x14ac:dyDescent="0.2">
@@ -35412,37 +35415,37 @@
         <v>743</v>
       </c>
       <c r="H256" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I256" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I256" s="60" t="s">
+      <c r="J256" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J256" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K256" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L256" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="M256" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="M256" s="7" t="s">
+      <c r="N256" s="7" t="s">
         <v>745</v>
       </c>
-      <c r="N256" s="7" t="s">
+      <c r="O256" s="7" t="s">
         <v>746</v>
       </c>
-      <c r="O256" s="7" t="s">
-        <v>747</v>
-      </c>
       <c r="Q256" s="7" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="R256" s="7" t="s">
         <v>208</v>
       </c>
       <c r="S256" s="7" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="V256" s="7">
         <v>8</v>
@@ -35499,13 +35502,13 @@
         <v>507</v>
       </c>
       <c r="BI256" s="7" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="BJ256" s="7">
         <v>2018</v>
       </c>
       <c r="BK256" s="7" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="257" spans="2:63" x14ac:dyDescent="0.2">
@@ -35522,37 +35525,37 @@
         <v>743</v>
       </c>
       <c r="H257" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I257" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I257" s="60" t="s">
+      <c r="J257" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J257" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K257" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L257" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="M257" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="M257" s="7" t="s">
+      <c r="N257" s="7" t="s">
         <v>745</v>
       </c>
-      <c r="N257" s="7" t="s">
+      <c r="O257" s="7" t="s">
         <v>746</v>
       </c>
-      <c r="O257" s="7" t="s">
-        <v>747</v>
-      </c>
       <c r="Q257" s="7" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="R257" s="7" t="s">
         <v>208</v>
       </c>
       <c r="S257" s="7" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="V257" s="7">
         <v>33</v>
@@ -35609,13 +35612,13 @@
         <v>507</v>
       </c>
       <c r="BI257" s="7" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="BJ257" s="7">
         <v>2015</v>
       </c>
       <c r="BK257" s="7" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="258" spans="2:63" x14ac:dyDescent="0.2">
@@ -35632,31 +35635,31 @@
         <v>743</v>
       </c>
       <c r="H258" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I258" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I258" s="60" t="s">
+      <c r="J258" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J258" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K258" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L258" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="M258" s="7" t="s">
         <v>744</v>
       </c>
-      <c r="M258" s="7" t="s">
+      <c r="N258" s="7" t="s">
         <v>745</v>
       </c>
-      <c r="N258" s="7" t="s">
+      <c r="O258" s="7" t="s">
         <v>746</v>
       </c>
-      <c r="O258" s="7" t="s">
-        <v>747</v>
-      </c>
       <c r="Q258" s="7" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="R258" s="7" t="s">
         <v>208</v>
@@ -35710,13 +35713,13 @@
         <v>507</v>
       </c>
       <c r="BI258" s="7" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="BJ258" s="7">
         <v>2006</v>
       </c>
       <c r="BK258" s="7" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
     </row>
     <row r="259" spans="2:63" x14ac:dyDescent="0.2">
@@ -35733,31 +35736,31 @@
         <v>743</v>
       </c>
       <c r="H259" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I259" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I259" s="60" t="s">
+      <c r="J259" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J259" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K259" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="L259" s="7" t="s">
-        <v>744</v>
+        <v>853</v>
       </c>
       <c r="M259" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="N259" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="O259" s="7" t="s">
         <v>755</v>
       </c>
-      <c r="N259" s="7" t="s">
-        <v>746</v>
-      </c>
-      <c r="O259" s="7" t="s">
+      <c r="Q259" s="7" t="s">
         <v>756</v>
-      </c>
-      <c r="Q259" s="7" t="s">
-        <v>757</v>
       </c>
       <c r="R259" s="7" t="s">
         <v>208</v>
@@ -35811,13 +35814,13 @@
         <v>507</v>
       </c>
       <c r="BI259" s="7" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="BJ259" s="7">
         <v>2002</v>
       </c>
       <c r="BK259" s="7" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="260" spans="2:63" x14ac:dyDescent="0.2">
@@ -35831,22 +35834,22 @@
         <v>24</v>
       </c>
       <c r="E260" s="7" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F260" s="7" t="s">
         <v>24</v>
       </c>
       <c r="H260" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I260" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I260" s="60" t="s">
+      <c r="J260" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J260" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K260" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L260" s="7" t="s">
         <v>378</v>
@@ -35867,10 +35870,10 @@
         <v>263</v>
       </c>
       <c r="S260" s="7" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="T260" s="7" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="U260" s="7" t="s">
         <v>48</v>
@@ -35930,16 +35933,16 @@
         <v>14</v>
       </c>
       <c r="BH260" s="7" t="s">
+        <v>758</v>
+      </c>
+      <c r="BI260" s="7" t="s">
         <v>759</v>
-      </c>
-      <c r="BI260" s="7" t="s">
-        <v>760</v>
       </c>
       <c r="BJ260" s="7">
         <v>2025</v>
       </c>
       <c r="BK260" s="7" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="261" spans="2:63" x14ac:dyDescent="0.2">
@@ -35953,16 +35956,16 @@
         <v>38</v>
       </c>
       <c r="H261" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I261" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I261" s="60" t="s">
+      <c r="J261" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J261" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K261" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L261" s="7" t="s">
         <v>347</v>
@@ -35977,7 +35980,7 @@
         <v>590</v>
       </c>
       <c r="Q261" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="R261" s="7" t="s">
         <v>349</v>
@@ -35986,7 +35989,7 @@
         <v>702</v>
       </c>
       <c r="T261" s="7" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="U261" s="7" t="s">
         <v>17</v>
@@ -36046,7 +36049,7 @@
         <v>507</v>
       </c>
       <c r="BI261" s="7" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="BJ261" s="7">
         <v>2025</v>
@@ -36066,16 +36069,16 @@
         <v>24</v>
       </c>
       <c r="H262" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I262" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I262" s="60" t="s">
+      <c r="J262" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J262" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K262" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L262" s="7" t="s">
         <v>347</v>
@@ -36090,7 +36093,7 @@
         <v>590</v>
       </c>
       <c r="Q262" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="R262" s="7" t="s">
         <v>349</v>
@@ -36156,7 +36159,7 @@
         <v>507</v>
       </c>
       <c r="BI262" s="7" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="BJ262" s="7">
         <v>2025</v>
@@ -36173,16 +36176,16 @@
         <v>38</v>
       </c>
       <c r="H263" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I263" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I263" s="60" t="s">
+      <c r="J263" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J263" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K263" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L263" s="7" t="s">
         <v>347</v>
@@ -36197,7 +36200,7 @@
         <v>590</v>
       </c>
       <c r="Q263" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="R263" s="7" t="s">
         <v>349</v>
@@ -36206,7 +36209,7 @@
         <v>702</v>
       </c>
       <c r="T263" s="7" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="U263" s="7" t="s">
         <v>17</v>
@@ -36257,13 +36260,13 @@
         <v>507</v>
       </c>
       <c r="BI263" s="7" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="BJ263" s="7">
         <v>2025</v>
       </c>
       <c r="BK263" s="7" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="264" spans="2:63" x14ac:dyDescent="0.2">
@@ -36277,16 +36280,16 @@
         <v>38</v>
       </c>
       <c r="H264" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I264" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I264" s="60" t="s">
+      <c r="J264" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J264" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K264" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L264" s="7" t="s">
         <v>347</v>
@@ -36301,7 +36304,7 @@
         <v>590</v>
       </c>
       <c r="Q264" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="R264" s="7" t="s">
         <v>349</v>
@@ -36310,7 +36313,7 @@
         <v>702</v>
       </c>
       <c r="T264" s="7" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="U264" s="7" t="s">
         <v>17</v>
@@ -36364,7 +36367,7 @@
         <v>507</v>
       </c>
       <c r="BI264" s="7" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="BJ264" s="7">
         <v>2025</v>
@@ -36381,22 +36384,22 @@
         <v>24</v>
       </c>
       <c r="E265" s="7" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F265" s="7" t="s">
         <v>24</v>
       </c>
       <c r="H265" s="60" t="s">
+        <v>782</v>
+      </c>
+      <c r="I265" s="60" t="s">
         <v>783</v>
       </c>
-      <c r="I265" s="60" t="s">
+      <c r="J265" s="60" t="s">
         <v>784</v>
       </c>
-      <c r="J265" s="60" t="s">
-        <v>785</v>
-      </c>
       <c r="K265" s="60" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="L265" s="7" t="s">
         <v>347</v>
@@ -36411,7 +36414,7 @@
         <v>590</v>
       </c>
       <c r="Q265" s="7" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="R265" s="7" t="s">
         <v>349</v>
@@ -36474,13 +36477,13 @@
         <v>507</v>
       </c>
       <c r="BI265" s="7" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="BJ265" s="7">
         <v>2025</v>
       </c>
       <c r="BK265" s="7" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
   </sheetData>
